--- a/Luban/Datas/BulletPattern.xlsx
+++ b/Luban/Datas/BulletPattern.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>enemy_bullet_02</t>
+          <t>level1_midboss_sway_windmill_bullet</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1869,10 +1869,10 @@
         <v>360</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O22" s="7" t="b">
         <v>1</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>enemy_bullet_02</t>
+          <t>level1_midboss_sway_windmill_bullet</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1934,10 +1934,10 @@
         <v>360</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O23" s="7" t="b">
         <v>1</v>

--- a/Luban/Datas/BulletPattern.xlsx
+++ b/Luban/Datas/BulletPattern.xlsx
@@ -347,7 +347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1955,6 +1955,201 @@
         <v>0.04</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>boss_p1_fan_dense_5</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>enemy_bullet_01</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>main_3</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>boss_p2_s_windmill_dense</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>enemy_bullet_02</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>left1,right1,center</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>boss_p3_s_windmill_dense_big</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>enemy_bullet_02</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>left1,right1,center</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/BulletPattern.xlsx
+++ b/Luban/Datas/BulletPattern.xlsx
@@ -347,7 +347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -2150,6 +2150,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>level2_helicopter_slow_pair</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>level2_helicopter_bullet_29</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>left,right</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/BulletPattern.xlsx
+++ b/Luban/Datas/BulletPattern.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="1" r:id="Rc4b836c481254a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="1" r:id="R0d840c01d2464026"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2355,7 +2355,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>boss_02_p1_center_ring_5</x:v>
+        <x:v>boss_02_p1_center_ring_3</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>Ring</x:v>
@@ -2400,7 +2400,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R30" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S30" t="n">
         <x:v>0.12</x:v>
@@ -2442,7 +2442,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="M31" t="n">
-        <x:v>3.1</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="N31" t="n">
         <x:v>5.8</x:v>
@@ -2469,7 +2469,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>boss_02_p3_all_yellow_laser</x:v>
+        <x:v>boss_02_p3_side_laser</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>Single</x:v>
@@ -2478,7 +2478,7 @@
         <x:v>boss_02_yellow_laser</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>left,center,right</x:v>
+        <x:v>left1,right1</x:v>
       </x:c>
       <x:c r="G32" t="n">
         <x:v>0</x:v>
@@ -2502,7 +2502,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N32" t="n">
-        <x:v>2</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="O32" s="8" t="b">
         <x:v>0</x:v>
@@ -2522,60 +2522,24 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
-      <x:c r="B33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>boss_02_p3_all_ring</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>Ring</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>enemy_bullet_02</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>left,center,right</x:v>
-      </x:c>
-      <x:c r="G33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L33" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="M33" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="N33" t="n">
-        <x:v>4.8</x:v>
-      </x:c>
-      <x:c r="O33" s="8" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="Q33" s="8" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S33" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
+      <x:c r="M33"/>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
+      <x:c r="S33"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Datas/BulletPattern.xlsx
+++ b/Luban/Datas/BulletPattern.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="1" r:id="R0d840c01d2464026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulletPattern" sheetId="1" r:id="Rf4e51de065fa462c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2418,7 +2418,7 @@
         <x:v>Spiral</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>boss_s_windmill_bullet</x:v>
+        <x:v>enemy_bullet_01</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>center</x:v>
@@ -2451,16 +2451,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P31" t="n">
-        <x:v>-14</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="Q31" s="8" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R31" t="n">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S31" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
